--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20070" windowHeight="9540"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局（下）" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
     <t>随着亚波伦座椅的扶手上传出一声轻响，一股巨大的能量波动猛地席卷了他的身体，顺着整间手术室的墙壁扩散开来，惨白的灯光开始疯狂闪烁，每一次明暗交替都带着电流滋啦的炸响。</t>
   </si>
   <si>
-    <t>bgfade(sntzm_final(3)_57,1)</t>
+    <t>playsfx(ElectricShock)&amp;bgfade(sntzm_final(3)_57,1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=7</t>
@@ -711,7 +711,25 @@
     <t>不是我！</t>
   </si>
   <si>
-    <t>loadScript(盖亚之心（上）_3, 1)</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>盖亚之心（上）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_2, 2)</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_David; 层级=63; gotomainline=盖亚之心（上）_3</t>
@@ -1048,6 +1066,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -5274,7 +5297,7 @@
       <c r="J65" t="s">
         <v>15</v>
       </c>
-      <c r="K65" t="s">
+      <c r="K65" s="3" t="s">
         <v>225</v>
       </c>
       <c r="L65" t="s">

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="517">
   <si>
     <t>ID</t>
   </si>
@@ -622,6 +622,9 @@
   </si>
   <si>
     <t>克拉克挤进去半个身子，手电光束顺着她指尖的方向照去，果然在椅腿和地面接触的内侧，刻着一行由刚刚淌下的血渍拓出的一行小字。</t>
+  </si>
+  <si>
+    <t>charfadeout(L,1)&amp;bgfade(sntzm_final(3)_104,1)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=54</t>
@@ -720,7 +723,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>盖亚之心（上）</t>
+      <t>sntzm_gy(1)</t>
     </r>
     <r>
       <rPr>
@@ -728,7 +731,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>_2, 2)</t>
+      <t>, 2)</t>
     </r>
   </si>
   <si>
@@ -1066,11 +1069,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1079,7 +1077,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>终局（终）</t>
+      <t>sntzm_final(4)</t>
     </r>
     <r>
       <rPr>
@@ -1087,7 +1085,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>_3, 3)</t>
+      <t>, 3)</t>
     </r>
   </si>
   <si>
@@ -4956,15 +4954,15 @@
         <v>15</v>
       </c>
       <c r="K56" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="L56" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" t="s">
         <v>93</v>
@@ -4973,7 +4971,7 @@
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4982,7 +4980,7 @@
         <v>15</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4997,12 +4995,12 @@
         <v>146</v>
       </c>
       <c r="L57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" ht="40.5" spans="1:12">
       <c r="A58" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5011,7 +5009,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5020,7 +5018,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5035,12 +5033,12 @@
         <v>37</v>
       </c>
       <c r="L58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" t="s">
         <v>158</v>
@@ -5058,7 +5056,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5073,12 +5071,12 @@
         <v>146</v>
       </c>
       <c r="L59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" ht="30" spans="1:12">
       <c r="A60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B60" t="s">
         <v>121</v>
@@ -5096,7 +5094,7 @@
         <v>131</v>
       </c>
       <c r="G60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5111,12 +5109,12 @@
         <v>182</v>
       </c>
       <c r="L60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" ht="27" spans="1:12">
       <c r="A61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5134,7 +5132,7 @@
         <v>131</v>
       </c>
       <c r="G61" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5149,12 +5147,12 @@
         <v>186</v>
       </c>
       <c r="L61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" ht="40.5" spans="1:12">
       <c r="A62" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5172,7 +5170,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5184,15 +5182,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B63" t="s">
         <v>158</v>
@@ -5210,7 +5208,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5225,12 +5223,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B64" t="s">
         <v>50</v>
@@ -5248,7 +5246,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5263,12 +5261,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" ht="30" spans="1:12">
       <c r="A65" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B65" t="s">
         <v>121</v>
@@ -5286,7 +5284,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5298,15 +5296,15 @@
         <v>15</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L65" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" ht="54" spans="1:12">
       <c r="A66" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
         <v>50</v>
@@ -5324,7 +5322,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5339,12 +5337,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
         <v>22</v>
@@ -5362,7 +5360,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5382,7 +5380,7 @@
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5400,7 +5398,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5415,12 +5413,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="69" ht="55.5" spans="1:12">
       <c r="A69" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" t="s">
         <v>22</v>
@@ -5438,7 +5436,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5453,12 +5451,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" ht="30" spans="1:12">
       <c r="A70" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B70" t="s">
         <v>22</v>
@@ -5476,7 +5474,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5491,12 +5489,12 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" ht="54" spans="1:12">
       <c r="A71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B71" t="s">
         <v>22</v>
@@ -5514,7 +5512,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5529,12 +5527,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" ht="42" spans="1:12">
       <c r="A72" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5552,7 +5550,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5572,7 +5570,7 @@
     </row>
     <row r="73" ht="67.5" spans="1:12">
       <c r="A73" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
@@ -5590,7 +5588,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5605,12 +5603,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" ht="30" spans="1:12">
       <c r="A74" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B74" t="s">
         <v>50</v>
@@ -5628,7 +5626,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5643,12 +5641,12 @@
         <v>37</v>
       </c>
       <c r="L74" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75" ht="67.5" spans="1:12">
       <c r="A75" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5666,7 +5664,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5681,12 +5679,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
@@ -5704,7 +5702,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5724,7 +5722,7 @@
     </row>
     <row r="77" ht="42" spans="1:12">
       <c r="A77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B77" t="s">
         <v>22</v>
@@ -5742,7 +5740,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5757,12 +5755,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" ht="30" spans="1:12">
       <c r="A78" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5780,7 +5778,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5795,12 +5793,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" ht="69" spans="1:12">
       <c r="A79" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B79" t="s">
         <v>22</v>
@@ -5818,7 +5816,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5838,7 +5836,7 @@
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B80" t="s">
         <v>50</v>
@@ -5856,7 +5854,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5871,12 +5869,12 @@
         <v>37</v>
       </c>
       <c r="L80" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="81" ht="30" spans="1:12">
       <c r="A81" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B81" t="s">
         <v>22</v>
@@ -5894,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5914,7 +5912,7 @@
     </row>
     <row r="82" ht="40.5" spans="1:12">
       <c r="A82" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5932,7 +5930,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5952,7 +5950,7 @@
     </row>
     <row r="83" ht="42" spans="1:12">
       <c r="A83" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B83" t="s">
         <v>22</v>
@@ -5970,7 +5968,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5982,12 +5980,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6005,7 +6003,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6025,7 +6023,7 @@
     </row>
     <row r="85" ht="42" spans="1:12">
       <c r="A85" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B85" t="s">
         <v>22</v>
@@ -6043,7 +6041,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6058,12 +6056,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="86" ht="30" spans="1:12">
       <c r="A86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B86" t="s">
         <v>50</v>
@@ -6081,7 +6079,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6096,12 +6094,12 @@
         <v>37</v>
       </c>
       <c r="L86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B87" t="s">
         <v>22</v>
@@ -6119,7 +6117,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6134,12 +6132,12 @@
         <v>146</v>
       </c>
       <c r="L87" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="88" ht="30" spans="1:12">
       <c r="A88" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B88" t="s">
         <v>22</v>
@@ -6157,7 +6155,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6172,12 +6170,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="89" ht="30" spans="1:12">
       <c r="A89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6195,7 +6193,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6215,7 +6213,7 @@
     </row>
     <row r="90" ht="40.5" spans="1:12">
       <c r="A90" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B90" t="s">
         <v>22</v>
@@ -6233,7 +6231,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6248,12 +6246,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="91" ht="30" spans="1:12">
       <c r="A91" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B91" t="s">
         <v>22</v>
@@ -6271,7 +6269,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6286,12 +6284,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="92" ht="55.5" spans="1:12">
       <c r="A92" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6309,7 +6307,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6329,7 +6327,7 @@
     </row>
     <row r="93" ht="67.5" spans="1:12">
       <c r="A93" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6344,7 +6342,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6359,12 +6357,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="94" ht="54" spans="1:12">
       <c r="A94" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B94" t="s">
         <v>22</v>
@@ -6382,7 +6380,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6397,12 +6395,12 @@
         <v>146</v>
       </c>
       <c r="L94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B95" t="s">
         <v>93</v>
@@ -6417,10 +6415,10 @@
         <v>15</v>
       </c>
       <c r="F95" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G95" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6435,12 +6433,12 @@
         <v>182</v>
       </c>
       <c r="L95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="96" ht="40.5" spans="1:12">
       <c r="A96" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6455,10 +6453,10 @@
         <v>15</v>
       </c>
       <c r="F96" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G96" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6478,7 +6476,7 @@
     </row>
     <row r="97" ht="42" spans="1:12">
       <c r="A97" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B97" t="s">
         <v>22</v>
@@ -6496,7 +6494,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6511,12 +6509,12 @@
         <v>146</v>
       </c>
       <c r="L97" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="98" ht="69" spans="1:12">
       <c r="A98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6534,7 +6532,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6546,7 +6544,7 @@
         <v>15</v>
       </c>
       <c r="K98" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L98" t="s">
         <v>126</v>
@@ -6554,7 +6552,7 @@
     </row>
     <row r="99" ht="40.5" spans="1:12">
       <c r="A99" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B99" t="s">
         <v>22</v>
@@ -6572,7 +6570,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6587,12 +6585,12 @@
         <v>146</v>
       </c>
       <c r="L99" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="100" ht="30" spans="1:12">
       <c r="A100" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B100" t="s">
         <v>22</v>
@@ -6610,7 +6608,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6622,12 +6620,12 @@
         <v>15</v>
       </c>
       <c r="L100" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="101" ht="40.5" spans="1:12">
       <c r="A101" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -6645,7 +6643,7 @@
         <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H101" t="s">
         <v>15</v>
@@ -6665,7 +6663,7 @@
     </row>
     <row r="102" ht="43.5" spans="1:12">
       <c r="A102" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
@@ -6683,7 +6681,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -6698,12 +6696,12 @@
         <v>15</v>
       </c>
       <c r="L102" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="103" ht="54" spans="1:12">
       <c r="A103" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B103" t="s">
         <v>22</v>
@@ -6721,7 +6719,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H103" t="s">
         <v>15</v>
@@ -6736,12 +6734,12 @@
         <v>15</v>
       </c>
       <c r="L103" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="104" ht="30" spans="1:12">
       <c r="A104" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B104" t="s">
         <v>22</v>
@@ -6759,7 +6757,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H104" t="s">
         <v>15</v>
@@ -6774,12 +6772,12 @@
         <v>15</v>
       </c>
       <c r="L104" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="105" ht="55.5" spans="1:12">
       <c r="A105" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -6797,7 +6795,7 @@
         <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H105" t="s">
         <v>15</v>
@@ -6817,7 +6815,7 @@
     </row>
     <row r="106" ht="40.5" spans="1:12">
       <c r="A106" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
@@ -6835,7 +6833,7 @@
         <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H106" t="s">
         <v>15</v>
@@ -6847,10 +6845,10 @@
         <v>15</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L106" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -6871,47 +6869,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -6919,7 +6917,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -6927,66 +6925,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B15" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -7008,616 +7006,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D13" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C15" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E15" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B16" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C16" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D16" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E16" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F16" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B17" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C17" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D17" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F17" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B18" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D18" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E18" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B19" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C19" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D19" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E19" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F19" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B20" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C20" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D20" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E20" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F20" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C21" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B22" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C22" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B24" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C24" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D24" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E24" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F24" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B25" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C25" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D25" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E25" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F25" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B26" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C26" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D26" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B27" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C27" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D27" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E27" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B28" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C28" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D28" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E28" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F28" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B29" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F29" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B30" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C30" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D30" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E30" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F30" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B31" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C31" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D31" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
